--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,225 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Goat Cheese</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>147.04</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>882.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mustard - Honey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Web/JP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - White</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sugar - Extra Fine</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PERF</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vegan Egg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>99.59</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>199.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FRZ Fruit - Peach (Sliced)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Spice - Italian Seasoning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Bowl (Smoothie)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H&amp;M/JP</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cup - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
